--- a/nir_gender_metrics.xlsx
+++ b/nir_gender_metrics.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="43">
   <si>
     <t>GENDER DATASET / EXPERIMENTS ON NUMERIC DESCRETIZATION EFFECT</t>
   </si>
@@ -117,6 +117,45 @@
   </si>
   <si>
     <t>0.4341</t>
+  </si>
+  <si>
+    <t>GLOVE EMBEDDING</t>
+  </si>
+  <si>
+    <t>DISC</t>
+  </si>
+  <si>
+    <t>no disc + cfg2</t>
+  </si>
+  <si>
+    <t>AGG TYPE</t>
+  </si>
+  <si>
+    <t>NOISY EMBEDDING</t>
+  </si>
+  <si>
+    <t>no disc</t>
+  </si>
+  <si>
+    <t>0.7703</t>
+  </si>
+  <si>
+    <t>0.7641</t>
+  </si>
+  <si>
+    <t>NOISY EMBEDDING + PLE</t>
+  </si>
+  <si>
+    <t>DISC/AGG</t>
+  </si>
+  <si>
+    <t>Quant/CAT</t>
+  </si>
+  <si>
+    <t>SingleTree/SUM</t>
+  </si>
+  <si>
+    <t>SingleTree/MEAN</t>
   </si>
 </sst>
 </file>
@@ -130,14 +169,7 @@
     <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -490,12 +522,156 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="23">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -616,137 +792,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -759,12 +935,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -774,13 +946,143 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1315,13 +1617,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.8571428571429" customWidth="1"/>
-    <col min="3" max="3" width="14.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="10.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="9.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="8.57142857142857" customWidth="1"/>
+    <col min="3" max="3" width="27.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="13.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -1396,7 +1699,7 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
     </row>
-    <row r="4" ht="15.75" spans="1:20">
+    <row r="4" spans="1:20">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -1436,20 +1739,20 @@
       <c r="E5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
@@ -1461,115 +1764,115 @@
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>0.849744319915771</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>0.888095378875732</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>0.83836841583252</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>0.864444732666016</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>0.4418</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>0.437</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>0.449466666666667</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>0.440333333333333</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>0.434333333333333</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>0.435666666666667</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>0.449</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>0.447333333333333</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
     </row>
     <row r="9" spans="3:8">
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1"/>
@@ -1608,16 +1911,16 @@
       <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>0.805921852588654</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>0.841415703296661</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>0.799817323684692</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>0.832950592041016</v>
       </c>
     </row>
@@ -1626,16 +1929,16 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>0.439066666666667</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>0.437466666666667</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>0.4402</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>0.4448</v>
       </c>
     </row>
@@ -1644,36 +1947,36 @@
       <c r="B15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>0.436333333333333</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>0.431333333333333</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="5">
         <v>0.438333333333333</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>0.431</v>
       </c>
     </row>
     <row r="16" spans="3:6">
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="1"/>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1"/>
@@ -1712,16 +2015,16 @@
       <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>0.758886635303497</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>0.79035359621048</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>0.73483282327652</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>0.774720668792725</v>
       </c>
     </row>
@@ -1730,16 +2033,16 @@
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>0.441133333333333</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>0.426533333333333</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>0.437666666666667</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>0.436733333333333</v>
       </c>
     </row>
@@ -1748,16 +2051,16 @@
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>0.441333333333333</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>0.429</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>0.428666666666667</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>0.439333333333333</v>
       </c>
     </row>
@@ -1871,11 +2174,11 @@
         <v>14</v>
       </c>
       <c r="M27" s="2"/>
-      <c r="N27" s="14" t="s">
+      <c r="N27" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
+      <c r="O27" s="57"/>
+      <c r="P27" s="57"/>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="2" t="s">
@@ -1884,116 +2187,116 @@
       <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>0.758886635303497</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>0.832981050014496</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>0.555599987506866</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>0.714621603488922</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>0.872716128826141</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>0.652424037456512</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="4">
         <v>0.688142061233521</v>
       </c>
-      <c r="J28" s="5">
+      <c r="J28" s="4">
         <v>0.827830016613007</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="4">
         <v>0.558118641376495</v>
       </c>
-      <c r="L28" s="5">
+      <c r="L28" s="4">
         <v>0.696921169757843</v>
       </c>
       <c r="M28" s="2"/>
-      <c r="N28" s="14" t="s">
+      <c r="N28" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="O28" s="14"/>
-      <c r="P28" s="14"/>
+      <c r="O28" s="57"/>
+      <c r="P28" s="57"/>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>0.441133333333333</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>0.436</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>0.433533333333333</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>0.4446</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>0.427866666666667</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="4">
         <v>0.423133333333333</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="4">
         <v>0.428066666666667</v>
       </c>
-      <c r="J29" s="5">
+      <c r="J29" s="4">
         <v>0.438733333333333</v>
       </c>
-      <c r="K29" s="5">
+      <c r="K29" s="4">
         <v>0.4254</v>
       </c>
-      <c r="L29" s="5">
+      <c r="L29" s="4">
         <v>0.425266666666667</v>
       </c>
       <c r="M29" s="2"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>0.441333333333333</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>0.442666666666667</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>0.434666666666667</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>0.436</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>0.432333333333333</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="4">
         <v>0.424666666666667</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="4">
         <v>0.416666666666667</v>
       </c>
-      <c r="J30" s="5">
+      <c r="J30" s="4">
         <v>0.438666666666667</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="4">
         <v>0.421</v>
       </c>
-      <c r="L30" s="5">
+      <c r="L30" s="4">
         <v>0.43</v>
       </c>
       <c r="M30" s="2"/>
@@ -2002,16 +2305,16 @@
       <c r="P30" s="2"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
@@ -2042,8 +2345,529 @@
         <v>29</v>
       </c>
     </row>
+    <row r="40" ht="15.75"/>
+    <row r="41" spans="2:13">
+      <c r="B41" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="58"/>
+    </row>
+    <row r="42" spans="2:13">
+      <c r="B42" s="11"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="59"/>
+    </row>
+    <row r="43" spans="2:13">
+      <c r="B43" s="12"/>
+      <c r="C43" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="1"/>
+      <c r="M43" s="59"/>
+    </row>
+    <row r="44" spans="2:13">
+      <c r="B44" s="12"/>
+      <c r="C44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13">
+      <c r="B45" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="16">
+        <v>0.758886635303497</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0.832981050014496</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0.555599987506866</v>
+      </c>
+      <c r="G45" s="4">
+        <v>0.714621603488922</v>
+      </c>
+      <c r="H45" s="17">
+        <v>0.872716128826141</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0.652424037456512</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0.688142061233521</v>
+      </c>
+      <c r="K45" s="17">
+        <v>0.827830016613007</v>
+      </c>
+      <c r="L45" s="4">
+        <v>0.558118641376495</v>
+      </c>
+      <c r="M45" s="61">
+        <v>0.696921169757843</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13">
+      <c r="B46" s="12"/>
+      <c r="C46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="16">
+        <v>0.771133333333333</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0.796</v>
+      </c>
+      <c r="F46" s="4">
+        <v>0.743533333333333</v>
+      </c>
+      <c r="G46" s="4">
+        <v>0.7546</v>
+      </c>
+      <c r="H46" s="17">
+        <v>0.807866666666667</v>
+      </c>
+      <c r="I46" s="4">
+        <v>0.753133333333333</v>
+      </c>
+      <c r="J46" s="4">
+        <v>0.768066666666667</v>
+      </c>
+      <c r="K46" s="17">
+        <v>0.788733333333333</v>
+      </c>
+      <c r="L46" s="4">
+        <v>0.7454</v>
+      </c>
+      <c r="M46" s="61">
+        <v>0.735266666666667</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" spans="2:13">
+      <c r="B47" s="18"/>
+      <c r="C47" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="20">
+        <v>0.771333333333333</v>
+      </c>
+      <c r="E47" s="21">
+        <v>0.792666666666667</v>
+      </c>
+      <c r="F47" s="21">
+        <v>0.734666666666667</v>
+      </c>
+      <c r="G47" s="21">
+        <v>0.756</v>
+      </c>
+      <c r="H47" s="22">
+        <v>0.792333333333333</v>
+      </c>
+      <c r="I47" s="21">
+        <v>0.744666666666667</v>
+      </c>
+      <c r="J47" s="21">
+        <v>0.756666666666667</v>
+      </c>
+      <c r="K47" s="22">
+        <v>0.788666666666667</v>
+      </c>
+      <c r="L47" s="21">
+        <v>0.741</v>
+      </c>
+      <c r="M47" s="62">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13">
+      <c r="B48" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="63"/>
+    </row>
+    <row r="49" spans="2:13">
+      <c r="B49" s="25"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="64"/>
+    </row>
+    <row r="50" spans="2:13">
+      <c r="B50" s="27"/>
+      <c r="C50" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="L50" s="1"/>
+      <c r="M50" s="59"/>
+    </row>
+    <row r="51" spans="2:13">
+      <c r="B51" s="27"/>
+      <c r="C51" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="K51" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" s="60" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13">
+      <c r="B52" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="35">
+        <v>0.83836841583252</v>
+      </c>
+      <c r="F52" s="36">
+        <v>0.73483282327652</v>
+      </c>
+      <c r="G52" s="36">
+        <v>0.799817323684692</v>
+      </c>
+      <c r="H52" s="37">
+        <v>0.888095378875732</v>
+      </c>
+      <c r="I52" s="65">
+        <v>0.79035359621048</v>
+      </c>
+      <c r="J52" s="65">
+        <v>0.841415703296661</v>
+      </c>
+      <c r="K52" s="35">
+        <v>0.849744319915771</v>
+      </c>
+      <c r="L52" s="36">
+        <v>0.758886635303497</v>
+      </c>
+      <c r="M52" s="66">
+        <v>0.805921852588654</v>
+      </c>
+    </row>
+    <row r="53" spans="2:13">
+      <c r="B53" s="12"/>
+      <c r="C53" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="38">
+        <v>0.809466666666667</v>
+      </c>
+      <c r="F53" s="39">
+        <v>0.777666666666667</v>
+      </c>
+      <c r="G53" s="40">
+        <v>0.7802</v>
+      </c>
+      <c r="H53" s="41">
+        <v>0.817</v>
+      </c>
+      <c r="I53" s="39">
+        <v>0.776533333333333</v>
+      </c>
+      <c r="J53" s="39">
+        <v>0.787466666666667</v>
+      </c>
+      <c r="K53" s="41">
+        <v>0.8118</v>
+      </c>
+      <c r="L53" s="40">
+        <v>0.801133333333333</v>
+      </c>
+      <c r="M53" s="67">
+        <v>0.799066666666667</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" spans="2:13">
+      <c r="B54" s="18"/>
+      <c r="C54" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" s="43">
+        <v>0.799</v>
+      </c>
+      <c r="F54" s="44">
+        <v>0.768666666666667</v>
+      </c>
+      <c r="G54" s="45">
+        <v>0.778333333333333</v>
+      </c>
+      <c r="H54" s="46">
+        <v>0.805666666666667</v>
+      </c>
+      <c r="I54" s="44">
+        <v>0.769</v>
+      </c>
+      <c r="J54" s="44">
+        <v>0.771333333333333</v>
+      </c>
+      <c r="K54" s="46">
+        <v>0.794333333333333</v>
+      </c>
+      <c r="L54" s="45">
+        <v>0.791333333333333</v>
+      </c>
+      <c r="M54" s="68">
+        <v>0.786333333333333</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
+      <c r="B55" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
+      <c r="L55" s="48"/>
+      <c r="M55" s="69"/>
+    </row>
+    <row r="56" spans="2:13">
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="64"/>
+    </row>
+    <row r="57" spans="2:13">
+      <c r="B57" s="49"/>
+      <c r="C57" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>40</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="64"/>
+    </row>
+    <row r="58" spans="2:13">
+      <c r="B58" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="17">
+        <v>0.864444732666016</v>
+      </c>
+      <c r="E58" s="4">
+        <v>0.832950592041016</v>
+      </c>
+      <c r="F58" s="51">
+        <v>0.774720668792725</v>
+      </c>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="64"/>
+    </row>
+    <row r="59" spans="2:13">
+      <c r="B59" s="49"/>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="17">
+        <v>0.805333333333333</v>
+      </c>
+      <c r="E59" s="4">
+        <v>0.7948</v>
+      </c>
+      <c r="F59" s="51">
+        <v>0.776733333333333</v>
+      </c>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="70"/>
+      <c r="M59" s="64"/>
+    </row>
+    <row r="60" ht="15.75" spans="2:13">
+      <c r="B60" s="52"/>
+      <c r="C60" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="22">
+        <v>0.797333333333333</v>
+      </c>
+      <c r="E60" s="21">
+        <v>0.791</v>
+      </c>
+      <c r="F60" s="54">
+        <v>0.769333333333333</v>
+      </c>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="71"/>
+      <c r="K60" s="55"/>
+      <c r="L60" s="71"/>
+      <c r="M60" s="72"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="36">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="A4:B4"/>
@@ -2067,9 +2891,19 @@
     <mergeCell ref="N27:P27"/>
     <mergeCell ref="N28:P28"/>
     <mergeCell ref="N29:P29"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="K50:M50"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A24:L25"/>
     <mergeCell ref="A32:C33"/>
+    <mergeCell ref="B41:M42"/>
+    <mergeCell ref="B48:M49"/>
+    <mergeCell ref="B55:F56"/>
+    <mergeCell ref="G55:M60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
